--- a/research/traditional_assets/database/data/sweden/sweden_air_transport.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_air_transport.xlsx
@@ -588,118 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.188</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.2740476337005354</v>
+        <v>-0.06193432049103582</v>
       </c>
       <c r="H2">
-        <v>-0.2740476337005354</v>
+        <v>-0.06193432049103582</v>
       </c>
       <c r="I2">
-        <v>-0.3840851744722752</v>
+        <v>-0.1063564171030274</v>
       </c>
       <c r="J2">
-        <v>-0.3840851744722752</v>
+        <v>-0.1063564171030274</v>
       </c>
       <c r="K2">
-        <v>-759.4</v>
+        <v>-638.6</v>
       </c>
       <c r="L2">
-        <v>-0.4673518370361253</v>
+        <v>-0.2214516073100531</v>
       </c>
       <c r="M2">
-        <v>31.9</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.03113410111262932</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.04200684751119305</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>31.9</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.03113410111262932</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.04200684751119305</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>496.9</v>
+        <v>784.2</v>
       </c>
       <c r="V2">
-        <v>0.4849697442904548</v>
+        <v>2.449094316052467</v>
       </c>
       <c r="W2">
-        <v>-0.6433957468440227</v>
+        <v>-0.8550006694336592</v>
       </c>
       <c r="X2">
-        <v>0.1645424404071122</v>
+        <v>0.5487548625004646</v>
       </c>
       <c r="Y2">
-        <v>-0.8079381872511349</v>
+        <v>-1.403755531934124</v>
       </c>
       <c r="Z2">
-        <v>0.4619605390345141</v>
+        <v>0.7196296666001197</v>
       </c>
       <c r="AA2">
-        <v>-0.1774321942343777</v>
+        <v>-0.07653723298063486</v>
       </c>
       <c r="AB2">
-        <v>0.09288910549494782</v>
+        <v>0.2449514267616029</v>
       </c>
       <c r="AC2">
-        <v>-0.2703212997293255</v>
+        <v>-0.3214886597422377</v>
       </c>
       <c r="AD2">
-        <v>3832.8</v>
+        <v>4124.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3832.8</v>
+        <v>4124.7</v>
       </c>
       <c r="AG2">
-        <v>3335.9</v>
+        <v>3340.5</v>
       </c>
       <c r="AH2">
-        <v>0.7890641083707334</v>
+        <v>0.9279623838556549</v>
       </c>
       <c r="AI2">
-        <v>0.8369107146756338</v>
+        <v>0.9835467486944702</v>
       </c>
       <c r="AJ2">
-        <v>0.765026946451095</v>
+        <v>0.9125303903624991</v>
       </c>
       <c r="AK2">
-        <v>0.8170618203193887</v>
+        <v>0.979762428508579</v>
       </c>
       <c r="AL2">
-        <v>140.3</v>
+        <v>152.8</v>
       </c>
       <c r="AM2">
-        <v>137.97</v>
+        <v>133</v>
       </c>
       <c r="AN2">
-        <v>-8.607231080170672</v>
+        <v>-23.0946248600224</v>
       </c>
       <c r="AO2">
-        <v>-4.448325017818959</v>
+        <v>-2.007198952879581</v>
       </c>
       <c r="AP2">
-        <v>-7.491354143274197</v>
+        <v>-18.70380739081747</v>
       </c>
       <c r="AQ2">
-        <v>-4.523447126186852</v>
+        <v>-2.306015037593985</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.188</v>
+        <v>-0.05690000000000001</v>
       </c>
       <c r="G3">
-        <v>-0.2740476337005354</v>
+        <v>-0.06193432049103582</v>
       </c>
       <c r="H3">
-        <v>-0.2740476337005354</v>
+        <v>-0.06193432049103582</v>
       </c>
       <c r="I3">
-        <v>-0.3840851744722752</v>
+        <v>-0.1063564171030274</v>
       </c>
       <c r="J3">
-        <v>-0.3840851744722752</v>
+        <v>-0.1063564171030274</v>
       </c>
       <c r="K3">
-        <v>-759.4</v>
+        <v>-638.6</v>
       </c>
       <c r="L3">
-        <v>-0.4673518370361253</v>
+        <v>-0.2214516073100531</v>
       </c>
       <c r="M3">
-        <v>31.9</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03113410111262932</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.04200684751119305</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>31.9</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03113410111262932</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.04200684751119305</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>496.9</v>
+        <v>784.2</v>
       </c>
       <c r="V3">
-        <v>0.4849697442904548</v>
+        <v>2.449094316052467</v>
       </c>
       <c r="W3">
-        <v>-0.6433957468440227</v>
+        <v>-0.8550006694336592</v>
       </c>
       <c r="X3">
-        <v>0.1645424404071122</v>
+        <v>0.5487548625004646</v>
       </c>
       <c r="Y3">
-        <v>-0.8079381872511349</v>
+        <v>-1.403755531934124</v>
       </c>
       <c r="Z3">
-        <v>0.4619605390345141</v>
+        <v>0.7196296666001197</v>
       </c>
       <c r="AA3">
-        <v>-0.1774321942343777</v>
+        <v>-0.07653723298063486</v>
       </c>
       <c r="AB3">
-        <v>0.09288910549494782</v>
+        <v>0.2449514267616029</v>
       </c>
       <c r="AC3">
-        <v>-0.2703212997293255</v>
+        <v>-0.3214886597422377</v>
       </c>
       <c r="AD3">
-        <v>3832.8</v>
+        <v>4124.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3832.8</v>
+        <v>4124.7</v>
       </c>
       <c r="AG3">
-        <v>3335.9</v>
+        <v>3340.5</v>
       </c>
       <c r="AH3">
-        <v>0.7890641083707334</v>
+        <v>0.9279623838556549</v>
       </c>
       <c r="AI3">
-        <v>0.8369107146756338</v>
+        <v>0.9835467486944702</v>
       </c>
       <c r="AJ3">
-        <v>0.765026946451095</v>
+        <v>0.9125303903624991</v>
       </c>
       <c r="AK3">
-        <v>0.8170618203193887</v>
+        <v>0.979762428508579</v>
       </c>
       <c r="AL3">
-        <v>140.3</v>
+        <v>152.8</v>
       </c>
       <c r="AM3">
-        <v>137.97</v>
+        <v>133</v>
       </c>
       <c r="AN3">
-        <v>-8.607231080170672</v>
+        <v>-23.0946248600224</v>
       </c>
       <c r="AO3">
-        <v>-4.448325017818959</v>
+        <v>-2.007198952879581</v>
       </c>
       <c r="AP3">
-        <v>-7.491354143274197</v>
+        <v>-18.70380739081747</v>
       </c>
       <c r="AQ3">
-        <v>-4.523447126186852</v>
+        <v>-2.306015037593985</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_air_transport.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_air_transport.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.05690000000000001</v>
+        <v>-0.0123</v>
       </c>
       <c r="G2">
-        <v>-0.06193432049103582</v>
+        <v>-0.04161791298798</v>
       </c>
       <c r="H2">
-        <v>-0.06193432049103582</v>
+        <v>-0.04161791298798</v>
       </c>
       <c r="I2">
-        <v>-0.1063564171030274</v>
+        <v>-0.06821082863525156</v>
       </c>
       <c r="J2">
-        <v>-0.1063564171030274</v>
+        <v>-0.06821082863525156</v>
       </c>
       <c r="K2">
-        <v>-638.6</v>
+        <v>-509.9</v>
       </c>
       <c r="L2">
-        <v>-0.2214516073100531</v>
+        <v>-0.1355972768854377</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>784.2</v>
+        <v>551</v>
       </c>
       <c r="V2">
-        <v>2.449094316052467</v>
-      </c>
-      <c r="W2">
-        <v>-0.8550006694336592</v>
+        <v>29.94565217391305</v>
       </c>
       <c r="X2">
-        <v>0.5487548625004646</v>
-      </c>
-      <c r="Y2">
-        <v>-1.403755531934124</v>
-      </c>
-      <c r="Z2">
-        <v>0.7196296666001197</v>
-      </c>
-      <c r="AA2">
-        <v>-0.07653723298063486</v>
+        <v>6.142814521678585</v>
       </c>
       <c r="AB2">
-        <v>0.2449514267616029</v>
-      </c>
-      <c r="AC2">
-        <v>-0.3214886597422377</v>
+        <v>0.08874624321948395</v>
       </c>
       <c r="AD2">
-        <v>4124.7</v>
+        <v>3800.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4124.7</v>
+        <v>3800.5</v>
       </c>
       <c r="AG2">
-        <v>3340.5</v>
+        <v>3249.5</v>
       </c>
       <c r="AH2">
-        <v>0.9279623838556549</v>
+        <v>0.9951818586503967</v>
       </c>
       <c r="AI2">
-        <v>0.9835467486944702</v>
+        <v>1.167947141979103</v>
       </c>
       <c r="AJ2">
-        <v>0.9125303903624991</v>
+        <v>0.9943694727500841</v>
       </c>
       <c r="AK2">
-        <v>0.979762428508579</v>
+        <v>1.202182759896411</v>
       </c>
       <c r="AL2">
-        <v>152.8</v>
+        <v>325.7</v>
       </c>
       <c r="AM2">
-        <v>133</v>
+        <v>234.8</v>
       </c>
       <c r="AN2">
-        <v>-23.0946248600224</v>
+        <v>-24.28434504792332</v>
       </c>
       <c r="AO2">
-        <v>-2.007198952879581</v>
+        <v>-0.7875345409886398</v>
       </c>
       <c r="AP2">
-        <v>-18.70380739081747</v>
+        <v>-20.76357827476038</v>
       </c>
       <c r="AQ2">
-        <v>-2.306015037593985</v>
+        <v>-1.092419080068143</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +701,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.05690000000000001</v>
+        <v>-0.0123</v>
       </c>
       <c r="G3">
-        <v>-0.06193432049103582</v>
+        <v>-0.04161791298798</v>
       </c>
       <c r="H3">
-        <v>-0.06193432049103582</v>
+        <v>-0.04161791298798</v>
       </c>
       <c r="I3">
-        <v>-0.1063564171030274</v>
+        <v>-0.06821082863525156</v>
       </c>
       <c r="J3">
-        <v>-0.1063564171030274</v>
+        <v>-0.06821082863525156</v>
       </c>
       <c r="K3">
-        <v>-638.6</v>
+        <v>-509.9</v>
       </c>
       <c r="L3">
-        <v>-0.2214516073100531</v>
+        <v>-0.1355972768854377</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +743,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>784.2</v>
+        <v>551</v>
       </c>
       <c r="V3">
-        <v>2.449094316052467</v>
-      </c>
-      <c r="W3">
-        <v>-0.8550006694336592</v>
+        <v>29.94565217391305</v>
       </c>
       <c r="X3">
-        <v>0.5487548625004646</v>
-      </c>
-      <c r="Y3">
-        <v>-1.403755531934124</v>
-      </c>
-      <c r="Z3">
-        <v>0.7196296666001197</v>
-      </c>
-      <c r="AA3">
-        <v>-0.07653723298063486</v>
+        <v>6.142814521678585</v>
       </c>
       <c r="AB3">
-        <v>0.2449514267616029</v>
-      </c>
-      <c r="AC3">
-        <v>-0.3214886597422377</v>
+        <v>0.08874624321948395</v>
       </c>
       <c r="AD3">
-        <v>4124.7</v>
+        <v>3800.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4124.7</v>
+        <v>3800.5</v>
       </c>
       <c r="AG3">
-        <v>3340.5</v>
+        <v>3249.5</v>
       </c>
       <c r="AH3">
-        <v>0.9279623838556549</v>
+        <v>0.9951818586503967</v>
       </c>
       <c r="AI3">
-        <v>0.9835467486944702</v>
+        <v>1.167947141979103</v>
       </c>
       <c r="AJ3">
-        <v>0.9125303903624991</v>
+        <v>0.9943694727500841</v>
       </c>
       <c r="AK3">
-        <v>0.979762428508579</v>
+        <v>1.202182759896411</v>
       </c>
       <c r="AL3">
-        <v>152.8</v>
+        <v>325.7</v>
       </c>
       <c r="AM3">
-        <v>133</v>
+        <v>234.8</v>
       </c>
       <c r="AN3">
-        <v>-23.0946248600224</v>
+        <v>-24.28434504792332</v>
       </c>
       <c r="AO3">
-        <v>-2.007198952879581</v>
+        <v>-0.7875345409886398</v>
       </c>
       <c r="AP3">
-        <v>-18.70380739081747</v>
+        <v>-20.76357827476038</v>
       </c>
       <c r="AQ3">
-        <v>-2.306015037593985</v>
+        <v>-1.092419080068143</v>
       </c>
     </row>
   </sheetData>
